--- a/data/base/Backlog_38.xlsx
+++ b/data/base/Backlog_38.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CD5F83-0BE6-4930-B0B4-DDADEBF4F20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD418C4-321F-48F3-8D3B-3519881F1BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
@@ -25,101 +25,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="27">
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>2026-08-07 13:26:10</t>
-  </si>
-  <si>
     <t>Lourival Silva</t>
   </si>
   <si>
-    <t>2026-09-10 11:41:25</t>
-  </si>
-  <si>
     <t>Erick Silva</t>
   </si>
   <si>
-    <t>2026-09-10 17:36:48</t>
-  </si>
-  <si>
     <t>Jose Ortiz</t>
   </si>
   <si>
-    <t>2026-09-14 07:45:17</t>
-  </si>
-  <si>
-    <t>2026-09-14 09:30:03</t>
-  </si>
-  <si>
     <t>Guilherme Worel</t>
   </si>
   <si>
-    <t>2026-09-14 13:25:24</t>
-  </si>
-  <si>
-    <t>2026-09-15 12:15:15</t>
-  </si>
-  <si>
-    <t>2026-09-15 14:01:09</t>
-  </si>
-  <si>
-    <t>2026-09-16 08:49:46</t>
-  </si>
-  <si>
-    <t>2026-09-18 15:25:02</t>
-  </si>
-  <si>
-    <t>2026-09-22 10:42:03</t>
-  </si>
-  <si>
-    <t>2026-09-22 11:05:07</t>
-  </si>
-  <si>
     <t>Michel Pessoa</t>
   </si>
   <si>
-    <t>2026-09-22 11:10:25</t>
-  </si>
-  <si>
-    <t>2026-09-22 14:14:22</t>
-  </si>
-  <si>
-    <t>2026-09-22 14:46:43</t>
-  </si>
-  <si>
-    <t>2026-09-22 17:02:41</t>
-  </si>
-  <si>
-    <t>2026-09-23 06:01:04</t>
-  </si>
-  <si>
     <t>Alana Oliveira</t>
   </si>
   <si>
-    <t>2026-09-23 06:01:10</t>
-  </si>
-  <si>
-    <t>2026-09-23 06:02:02</t>
-  </si>
-  <si>
-    <t>2026-09-23 10:52:06</t>
-  </si>
-  <si>
-    <t>2026-09-23 10:58:56</t>
-  </si>
-  <si>
     <t>Emerson Simette</t>
   </si>
   <si>
     <t>Felipe Nascimento</t>
   </si>
   <si>
-    <t>2026-09-23 14:41:55</t>
-  </si>
-  <si>
     <t>Gabriel López</t>
   </si>
   <si>
@@ -159,28 +93,13 @@
     <t>Pendente</t>
   </si>
   <si>
-    <t>2026-09-10 14:46:21</t>
-  </si>
-  <si>
     <t>Mara Moraes</t>
   </si>
   <si>
-    <t>2026-09-21 13:03:52</t>
-  </si>
-  <si>
     <t>Anderson Giese</t>
   </si>
   <si>
-    <t>2026-09-21 13:47:27</t>
-  </si>
-  <si>
     <t>Gabriel Coelho</t>
-  </si>
-  <si>
-    <t>2026-09-21 17:09:24</t>
-  </si>
-  <si>
-    <t>2026-09-22 13:22:42</t>
   </si>
   <si>
     <t>SPN</t>
@@ -193,6 +112,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-416]mmm/yy"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -220,7 +142,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,12 +152,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -267,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -288,26 +204,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -654,7 +564,7 @@
     <col min="5" max="5" width="18.75" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.75" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="3" bestFit="1" customWidth="1"/>
@@ -662,45 +572,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5">
         <v>2026</v>
@@ -717,25 +627,25 @@
       <c r="G2" s="5">
         <v>25575</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>22</v>
+      <c r="H2" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I2" s="6">
         <v>46293</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C3" s="5">
         <v>2026</v>
@@ -752,25 +662,25 @@
       <c r="G3" s="5">
         <v>25576</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>24</v>
+      <c r="H3" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I3" s="6">
         <v>46293</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5">
         <v>2026</v>
@@ -787,25 +697,25 @@
       <c r="G4" s="5">
         <v>25577</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>25</v>
+      <c r="H4" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I4" s="6">
         <v>46293</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="5">
         <v>2026</v>
@@ -822,25 +732,25 @@
       <c r="G5" s="5">
         <v>24760</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>3</v>
+      <c r="H5" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I5" s="6">
         <v>46293</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5">
         <v>2026</v>
@@ -857,25 +767,25 @@
       <c r="G6" s="5">
         <v>24909</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>7</v>
+      <c r="H6" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I6" s="6">
         <v>46293</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="5">
         <v>2026</v>
@@ -892,25 +802,25 @@
       <c r="G7" s="5">
         <v>24965</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>10</v>
+      <c r="H7" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I7" s="6">
         <v>46293</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="5">
         <v>2026</v>
@@ -927,25 +837,25 @@
       <c r="G8" s="5">
         <v>25050</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>11</v>
+      <c r="H8" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I8" s="6">
         <v>46293</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="5">
         <v>2026</v>
@@ -962,25 +872,25 @@
       <c r="G9" s="5">
         <v>25058</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>12</v>
+      <c r="H9" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I9" s="6">
         <v>46293</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" s="5">
         <v>2026</v>
@@ -997,25 +907,25 @@
       <c r="G10" s="5">
         <v>25113</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>13</v>
+      <c r="H10" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I10" s="6">
         <v>46293</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5">
         <v>2026</v>
@@ -1032,25 +942,25 @@
       <c r="G11" s="5">
         <v>25325</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>14</v>
+      <c r="H11" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I11" s="6">
         <v>46293</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" s="5">
         <v>2026</v>
@@ -1067,25 +977,25 @@
       <c r="G12" s="5">
         <v>25517</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>15</v>
+      <c r="H12" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I12" s="6">
         <v>46293</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5">
         <v>2026</v>
@@ -1102,25 +1012,25 @@
       <c r="G13" s="5">
         <v>25523</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>18</v>
+      <c r="H13" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I13" s="6">
         <v>46293</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" s="5">
         <v>2026</v>
@@ -1137,25 +1047,25 @@
       <c r="G14" s="5">
         <v>25543</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>20</v>
+      <c r="H14" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I14" s="6">
         <v>46293</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C15" s="5">
         <v>2026</v>
@@ -1172,25 +1082,25 @@
       <c r="G15" s="5">
         <v>25622</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>27</v>
+      <c r="H15" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I15" s="6">
         <v>46293</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C16" s="5">
         <v>2026</v>
@@ -1207,25 +1117,25 @@
       <c r="G16" s="5">
         <v>25642</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>30</v>
+      <c r="H16" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I16" s="6">
         <v>46293</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C17" s="5">
         <v>2026</v>
@@ -1242,25 +1152,25 @@
       <c r="G17" s="5">
         <v>24939</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>8</v>
+      <c r="H17" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I17" s="6">
         <v>46293</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C18" s="5">
         <v>2026</v>
@@ -1277,25 +1187,25 @@
       <c r="G18" s="5">
         <v>24809</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>5</v>
+      <c r="H18" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I18" s="6">
         <v>46293</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="5">
         <v>2026</v>
@@ -1312,25 +1222,25 @@
       <c r="G19" s="5">
         <v>22680</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>1</v>
+      <c r="H19" s="13">
+        <v>46265.589861111112</v>
       </c>
       <c r="I19" s="6">
         <v>46293</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="5">
         <v>2026</v>
@@ -1347,25 +1257,25 @@
       <c r="G20" s="5">
         <v>25536</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>19</v>
+      <c r="H20" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I20" s="6">
         <v>46293</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="5">
         <v>2026</v>
@@ -1382,25 +1292,25 @@
       <c r="G21" s="5">
         <v>25561</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>21</v>
+      <c r="H21" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I21" s="6">
         <v>46293</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5">
         <v>2026</v>
@@ -1417,25 +1327,25 @@
       <c r="G22" s="5">
         <v>25521</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>16</v>
+      <c r="H22" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I22" s="6">
         <v>46293</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5">
         <v>2026</v>
@@ -1452,17 +1362,17 @@
       <c r="G23" s="5">
         <v>25621</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>26</v>
+      <c r="H23" s="13">
+        <v>46275.647430555553</v>
       </c>
       <c r="I23" s="6">
         <v>46293</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1480,253 +1390,253 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.875" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="10" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="13" t="s">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="13" t="s">
-        <v>41</v>
+      <c r="K1" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="8">
-        <v>38</v>
-      </c>
-      <c r="E2" s="9">
-        <v>46293</v>
-      </c>
-      <c r="F2" s="9">
-        <v>46297</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="A2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="9">
+        <v>38</v>
+      </c>
+      <c r="E2" s="10">
+        <v>46293</v>
+      </c>
+      <c r="F2" s="10">
+        <v>46297</v>
+      </c>
+      <c r="G2" s="9">
         <v>25423</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="9">
-        <v>46293</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>53</v>
+      <c r="H2" s="13">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I2" s="10">
+        <v>46293</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="8">
-        <v>38</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46293</v>
-      </c>
-      <c r="F3" s="9">
-        <v>46297</v>
-      </c>
-      <c r="G3" s="8">
+      <c r="A3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="9">
+        <v>38</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46293</v>
+      </c>
+      <c r="F3" s="10">
+        <v>46297</v>
+      </c>
+      <c r="G3" s="9">
         <v>25463</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="9">
-        <v>46293</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>53</v>
+      <c r="H3" s="13">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I3" s="10">
+        <v>46293</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="8">
-        <v>38</v>
-      </c>
-      <c r="E4" s="9">
-        <v>46293</v>
-      </c>
-      <c r="F4" s="9">
-        <v>46297</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="A4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="9">
+        <v>38</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46293</v>
+      </c>
+      <c r="F4" s="10">
+        <v>46297</v>
+      </c>
+      <c r="G4" s="9">
         <v>25432</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="9">
-        <v>46293</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>53</v>
+      <c r="H4" s="13">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I4" s="10">
+        <v>46293</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="8">
-        <v>38</v>
-      </c>
-      <c r="E5" s="9">
-        <v>46293</v>
-      </c>
-      <c r="F5" s="9">
-        <v>46297</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="A5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="9">
+        <v>38</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46293</v>
+      </c>
+      <c r="F5" s="10">
+        <v>46297</v>
+      </c>
+      <c r="G5" s="9">
         <v>24782</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="9">
-        <v>46293</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>53</v>
+      <c r="H5" s="13">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I5" s="10">
+        <v>46293</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="8">
-        <v>38</v>
-      </c>
-      <c r="E6" s="9">
-        <v>46293</v>
-      </c>
-      <c r="F6" s="9">
-        <v>46297</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="A6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="9">
+        <v>38</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46293</v>
+      </c>
+      <c r="F6" s="10">
+        <v>46297</v>
+      </c>
+      <c r="G6" s="9">
         <v>25528</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="9">
-        <v>46293</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>53</v>
+      <c r="H6" s="13">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I6" s="10">
+        <v>46293</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{04072895-7296-4D23-B9B6-05832E05733C}">

--- a/data/base/Backlog_38.xlsx
+++ b/data/base/Backlog_38.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD418C4-321F-48F3-8D3B-3519881F1BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B3F743-F2C0-42D0-A9D4-EE8208938654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="28">
   <si>
     <t>Status</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Willian Rios</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -183,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -191,19 +194,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -217,9 +210,10 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,17 +551,18 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -609,7 +604,7 @@
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5">
@@ -627,16 +622,16 @@
       <c r="G2" s="5">
         <v>25575</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I2" s="6">
         <v>46293</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -644,7 +639,7 @@
       <c r="A3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="5">
@@ -662,16 +657,16 @@
       <c r="G3" s="5">
         <v>25576</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I3" s="6">
         <v>46293</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -679,7 +674,7 @@
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5">
@@ -697,16 +692,16 @@
       <c r="G4" s="5">
         <v>25577</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I4" s="6">
         <v>46293</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -714,7 +709,7 @@
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="5">
@@ -732,7 +727,7 @@
       <c r="G5" s="5">
         <v>24760</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I5" s="6">
@@ -741,7 +736,7 @@
       <c r="J5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -749,7 +744,7 @@
       <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="5">
@@ -767,7 +762,7 @@
       <c r="G6" s="5">
         <v>24909</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I6" s="6">
@@ -776,7 +771,7 @@
       <c r="J6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -784,7 +779,7 @@
       <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="5">
@@ -802,7 +797,7 @@
       <c r="G7" s="5">
         <v>24965</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I7" s="6">
@@ -811,7 +806,7 @@
       <c r="J7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -819,7 +814,7 @@
       <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="5">
@@ -837,7 +832,7 @@
       <c r="G8" s="5">
         <v>25050</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I8" s="6">
@@ -846,7 +841,7 @@
       <c r="J8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -854,7 +849,7 @@
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="5">
@@ -872,7 +867,7 @@
       <c r="G9" s="5">
         <v>25058</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I9" s="6">
@@ -881,7 +876,7 @@
       <c r="J9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -889,7 +884,7 @@
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="5">
@@ -907,7 +902,7 @@
       <c r="G10" s="5">
         <v>25113</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I10" s="6">
@@ -916,7 +911,7 @@
       <c r="J10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -924,7 +919,7 @@
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="5">
@@ -942,7 +937,7 @@
       <c r="G11" s="5">
         <v>25325</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I11" s="6">
@@ -951,7 +946,7 @@
       <c r="J11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -959,7 +954,7 @@
       <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="5">
@@ -977,7 +972,7 @@
       <c r="G12" s="5">
         <v>25517</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I12" s="6">
@@ -986,7 +981,7 @@
       <c r="J12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -994,7 +989,7 @@
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C13" s="5">
@@ -1012,7 +1007,7 @@
       <c r="G13" s="5">
         <v>25523</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I13" s="6">
@@ -1021,7 +1016,7 @@
       <c r="J13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1029,7 +1024,7 @@
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="5">
@@ -1047,16 +1042,16 @@
       <c r="G14" s="5">
         <v>25543</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I14" s="6">
         <v>46293</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1064,7 +1059,7 @@
       <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="5">
@@ -1082,16 +1077,16 @@
       <c r="G15" s="5">
         <v>25622</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I15" s="6">
         <v>46293</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1099,7 +1094,7 @@
       <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="5">
@@ -1117,16 +1112,16 @@
       <c r="G16" s="5">
         <v>25642</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I16" s="6">
         <v>46293</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1134,7 +1129,7 @@
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="5">
@@ -1152,7 +1147,7 @@
       <c r="G17" s="5">
         <v>24939</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I17" s="6">
@@ -1161,7 +1156,7 @@
       <c r="J17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1169,7 +1164,7 @@
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="10" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="5">
@@ -1187,7 +1182,7 @@
       <c r="G18" s="5">
         <v>24809</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I18" s="6">
@@ -1196,7 +1191,7 @@
       <c r="J18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1204,7 +1199,7 @@
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="5">
@@ -1222,7 +1217,7 @@
       <c r="G19" s="5">
         <v>22680</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="9">
         <v>46265.589861111112</v>
       </c>
       <c r="I19" s="6">
@@ -1231,7 +1226,7 @@
       <c r="J19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1239,7 +1234,7 @@
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="5">
@@ -1257,16 +1252,16 @@
       <c r="G20" s="5">
         <v>25536</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I20" s="6">
         <v>46293</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1274,7 +1269,7 @@
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="5">
@@ -1292,7 +1287,7 @@
       <c r="G21" s="5">
         <v>25561</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I21" s="6">
@@ -1301,7 +1296,7 @@
       <c r="J21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1309,7 +1304,7 @@
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="5">
@@ -1327,7 +1322,7 @@
       <c r="G22" s="5">
         <v>25521</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I22" s="6">
@@ -1336,7 +1331,7 @@
       <c r="J22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1344,7 +1339,7 @@
       <c r="A23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="5">
@@ -1362,7 +1357,7 @@
       <c r="G23" s="5">
         <v>25621</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="9">
         <v>46275.647430555553</v>
       </c>
       <c r="I23" s="6">
@@ -1371,7 +1366,7 @@
       <c r="J23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1390,18 +1385,18 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.875" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="10" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1440,203 +1435,203 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="9">
-        <v>38</v>
-      </c>
-      <c r="E2" s="10">
-        <v>46293</v>
-      </c>
-      <c r="F2" s="10">
-        <v>46297</v>
-      </c>
-      <c r="G2" s="9">
+      <c r="C2" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="5">
+        <v>38</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46293</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46297</v>
+      </c>
+      <c r="G2" s="5">
         <v>25423</v>
       </c>
-      <c r="H2" s="13">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I2" s="10">
-        <v>46293</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="H2" s="9">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I2" s="6">
+        <v>46293</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="9">
-        <v>38</v>
-      </c>
-      <c r="E3" s="10">
-        <v>46293</v>
-      </c>
-      <c r="F3" s="10">
-        <v>46297</v>
-      </c>
-      <c r="G3" s="9">
+      <c r="C3" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="5">
+        <v>38</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46293</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46297</v>
+      </c>
+      <c r="G3" s="5">
         <v>25463</v>
       </c>
-      <c r="H3" s="13">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I3" s="10">
-        <v>46293</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="H3" s="9">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I3" s="6">
+        <v>46293</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="9">
-        <v>38</v>
-      </c>
-      <c r="E4" s="10">
-        <v>46293</v>
-      </c>
-      <c r="F4" s="10">
-        <v>46297</v>
-      </c>
-      <c r="G4" s="9">
+      <c r="C4" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="5">
+        <v>38</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46293</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46297</v>
+      </c>
+      <c r="G4" s="5">
         <v>25432</v>
       </c>
-      <c r="H4" s="13">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I4" s="10">
-        <v>46293</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="H4" s="9">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46293</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="9">
-        <v>38</v>
-      </c>
-      <c r="E5" s="10">
-        <v>46293</v>
-      </c>
-      <c r="F5" s="10">
-        <v>46297</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="C5" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="5">
+        <v>38</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46293</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46297</v>
+      </c>
+      <c r="G5" s="5">
         <v>24782</v>
       </c>
-      <c r="H5" s="13">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I5" s="10">
-        <v>46293</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="H5" s="9">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I5" s="6">
+        <v>46293</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="9">
-        <v>38</v>
-      </c>
-      <c r="E6" s="10">
-        <v>46293</v>
-      </c>
-      <c r="F6" s="10">
-        <v>46297</v>
-      </c>
-      <c r="G6" s="9">
+      <c r="C6" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="5">
+        <v>38</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46293</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46297</v>
+      </c>
+      <c r="G6" s="5">
         <v>25528</v>
       </c>
-      <c r="H6" s="13">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I6" s="10">
-        <v>46293</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="H6" s="9">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I6" s="6">
+        <v>46293</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{04072895-7296-4D23-B9B6-05832E05733C}">

--- a/data/base/Backlog_38.xlsx
+++ b/data/base/Backlog_38.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B3F743-F2C0-42D0-A9D4-EE8208938654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB6755B-71BE-425A-A1E7-9A3243055346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
     <sheet name="SPN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -145,7 +145,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,6 +155,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -186,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -214,6 +220,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,318 +725,318 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="5">
-        <v>38</v>
-      </c>
-      <c r="E5" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="C5" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="11">
+        <v>38</v>
+      </c>
+      <c r="E5" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F5" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G5" s="11">
         <v>24760</v>
       </c>
-      <c r="H5" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I5" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="H5" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I5" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="5">
-        <v>38</v>
-      </c>
-      <c r="E6" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="C6" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="11">
+        <v>38</v>
+      </c>
+      <c r="E6" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F6" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G6" s="11">
         <v>24909</v>
       </c>
-      <c r="H6" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I6" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="H6" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I6" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="5">
-        <v>38</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="C7" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="11">
+        <v>38</v>
+      </c>
+      <c r="E7" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F7" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G7" s="11">
         <v>24965</v>
       </c>
-      <c r="H7" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I7" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="H7" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I7" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="5">
-        <v>38</v>
-      </c>
-      <c r="E8" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="C8" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="11">
+        <v>38</v>
+      </c>
+      <c r="E8" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F8" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G8" s="11">
         <v>25050</v>
       </c>
-      <c r="H8" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I8" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="H8" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I8" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="5">
-        <v>38</v>
-      </c>
-      <c r="E9" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="C9" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="11">
+        <v>38</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F9" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G9" s="11">
         <v>25058</v>
       </c>
-      <c r="H9" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I9" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="H9" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I9" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="5">
-        <v>38</v>
-      </c>
-      <c r="E10" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="C10" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="11">
+        <v>38</v>
+      </c>
+      <c r="E10" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F10" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G10" s="11">
         <v>25113</v>
       </c>
-      <c r="H10" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I10" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="H10" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I10" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="5">
-        <v>38</v>
-      </c>
-      <c r="E11" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="C11" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="11">
+        <v>38</v>
+      </c>
+      <c r="E11" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F11" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G11" s="11">
         <v>25325</v>
       </c>
-      <c r="H11" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I11" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="H11" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I11" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="5">
-        <v>38</v>
-      </c>
-      <c r="E12" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="C12" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="11">
+        <v>38</v>
+      </c>
+      <c r="E12" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F12" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G12" s="11">
         <v>25517</v>
       </c>
-      <c r="H12" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I12" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="H12" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I12" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="5">
-        <v>38</v>
-      </c>
-      <c r="E13" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F13" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G13" s="5">
+      <c r="C13" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="11">
+        <v>38</v>
+      </c>
+      <c r="E13" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F13" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G13" s="11">
         <v>25523</v>
       </c>
-      <c r="H13" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I13" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="3" t="s">
+      <c r="H13" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I13" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="15" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1125,108 +1145,108 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="10" t="s">
+    <row r="17" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="5">
-        <v>38</v>
-      </c>
-      <c r="E17" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G17" s="5">
+      <c r="C17" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="11">
+        <v>38</v>
+      </c>
+      <c r="E17" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F17" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G17" s="11">
         <v>24939</v>
       </c>
-      <c r="H17" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I17" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="10" t="s">
+      <c r="H17" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I17" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="5">
-        <v>38</v>
-      </c>
-      <c r="E18" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G18" s="5">
+      <c r="C18" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="11">
+        <v>38</v>
+      </c>
+      <c r="E18" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F18" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G18" s="11">
         <v>24809</v>
       </c>
-      <c r="H18" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I18" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="10" t="s">
+      <c r="H18" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I18" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="5">
-        <v>38</v>
-      </c>
-      <c r="E19" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="C19" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="11">
+        <v>38</v>
+      </c>
+      <c r="E19" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F19" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G19" s="11">
         <v>22680</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="14">
         <v>46265.589861111112</v>
       </c>
-      <c r="I19" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="I19" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="15" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1265,113 +1285,113 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="10" t="s">
+    <row r="21" spans="1:11" s="16" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="5">
-        <v>38</v>
-      </c>
-      <c r="E21" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="C21" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="11">
+        <v>38</v>
+      </c>
+      <c r="E21" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F21" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G21" s="11">
         <v>25561</v>
       </c>
-      <c r="H21" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I21" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="10" t="s">
+      <c r="H21" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I21" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="5">
-        <v>38</v>
-      </c>
-      <c r="E22" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F22" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="C22" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="11">
+        <v>38</v>
+      </c>
+      <c r="E22" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F22" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G22" s="11">
         <v>25521</v>
       </c>
-      <c r="H22" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I22" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="10" t="s">
+      <c r="H22" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I22" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="5">
-        <v>38</v>
-      </c>
-      <c r="E23" s="6">
-        <v>46293</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46297</v>
-      </c>
-      <c r="G23" s="5">
+      <c r="C23" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="11">
+        <v>38</v>
+      </c>
+      <c r="E23" s="13">
+        <v>46293</v>
+      </c>
+      <c r="F23" s="13">
+        <v>46297</v>
+      </c>
+      <c r="G23" s="11">
         <v>25621</v>
       </c>
-      <c r="H23" s="9">
-        <v>46275.647430555553</v>
-      </c>
-      <c r="I23" s="6">
-        <v>46293</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="3" t="s">
+      <c r="H23" s="14">
+        <v>46275.647430555553</v>
+      </c>
+      <c r="I23" s="13">
+        <v>46293</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="15" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:K23" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
       <sortCondition ref="B1"/>
     </sortState>
@@ -1634,7 +1654,7 @@
       <c r="F12" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{04072895-7296-4D23-B9B6-05832E05733C}">
+  <autoFilter ref="A1:K6" xr:uid="{04072895-7296-4D23-B9B6-05832E05733C}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K7">
       <sortCondition ref="B1"/>
     </sortState>
